--- a/fichiers/Tableau_synthese_E4_BTS_SIO.xlsx
+++ b/fichiers/Tableau_synthese_E4_BTS_SIO.xlsx
@@ -1146,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:AQ33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2"/>
   <cols>
     <col width="70.44140625" customWidth="1" style="1" min="1" max="1"/>
@@ -1346,228 +1346,104 @@
       <c r="H8" s="51" t="n"/>
     </row>
     <row r="9" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A9" s="43" t="inlineStr">
-        <is>
-          <t>Mise en place d'une infrastructure virtualisée (VMware/VirtualBox) pour un environnement de test</t>
-        </is>
-      </c>
-      <c r="B9" s="44" t="inlineStr">
-        <is>
-          <t>01/09/25 au 30/09/25</t>
-        </is>
-      </c>
-      <c r="C9" s="46" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D9" s="46" t="inlineStr"/>
-      <c r="E9" s="17" t="inlineStr"/>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="47" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr"/>
+      <c r="A9" s="43" t="n"/>
+      <c r="B9" s="44" t="n"/>
+      <c r="C9" s="46" t="n"/>
+      <c r="D9" s="46" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="47" t="n"/>
+      <c r="H9" s="17" t="n"/>
     </row>
     <row r="10" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A10" s="43" t="inlineStr">
-        <is>
-          <t>Installation et configuration d'un serveur Windows Server (AD, DNS, DHCP)</t>
-        </is>
-      </c>
-      <c r="B10" s="44" t="inlineStr">
-        <is>
-          <t>01/10/25 au 15/10/25</t>
-        </is>
-      </c>
-      <c r="C10" s="46" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr"/>
-      <c r="E10" s="17" t="inlineStr"/>
-      <c r="F10" s="17" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr"/>
+      <c r="A10" s="43" t="n"/>
+      <c r="B10" s="44" t="n"/>
+      <c r="C10" s="46" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="n"/>
     </row>
     <row r="11" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A11" s="43" t="inlineStr">
-        <is>
-          <t>Déploiement d'un serveur Linux (Debian/Ubuntu) et administration via ligne de commande</t>
-        </is>
-      </c>
-      <c r="B11" s="44" t="inlineStr">
-        <is>
-          <t>16/10/25 au 31/10/25</t>
-        </is>
-      </c>
-      <c r="C11" s="46" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr"/>
-      <c r="F11" s="17" t="inlineStr"/>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H11" s="48" t="inlineStr"/>
+      <c r="A11" s="43" t="n"/>
+      <c r="B11" s="44" t="n"/>
+      <c r="C11" s="46" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="48" t="n"/>
     </row>
     <row r="12" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A12" s="43" t="inlineStr">
-        <is>
-          <t>Configuration d'un réseau local (VLAN, routage, switch) en environnement de test</t>
-        </is>
-      </c>
-      <c r="B12" s="44" t="inlineStr">
-        <is>
-          <t>01/11/25 au 15/11/25</t>
-        </is>
-      </c>
-      <c r="C12" s="46" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr"/>
-      <c r="E12" s="17" t="inlineStr"/>
-      <c r="F12" s="17" t="inlineStr"/>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr"/>
+      <c r="A12" s="43" t="n"/>
+      <c r="B12" s="44" t="n"/>
+      <c r="C12" s="46" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="17" t="n"/>
+      <c r="H12" s="17" t="n"/>
     </row>
     <row r="13" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A13" s="43" t="inlineStr">
-        <is>
-          <t>Mise en place d'une politique de sauvegarde et de restauration de données</t>
-        </is>
-      </c>
-      <c r="B13" s="44" t="inlineStr">
-        <is>
-          <t>16/11/25 au 30/11/25</t>
-        </is>
-      </c>
-      <c r="C13" s="46" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr"/>
-      <c r="E13" s="17" t="inlineStr"/>
-      <c r="F13" s="17" t="inlineStr"/>
-      <c r="G13" s="17" t="inlineStr"/>
-      <c r="H13" s="17" t="inlineStr"/>
+      <c r="A13" s="43" t="n"/>
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="46" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="17" t="n"/>
+      <c r="H13" s="17" t="n"/>
     </row>
     <row r="14" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A14" s="43" t="inlineStr">
-        <is>
-          <t>Création et gestion d'une base de connaissances pour le support utilisateurs</t>
-        </is>
-      </c>
-      <c r="B14" s="44" t="inlineStr">
-        <is>
-          <t>01/12/25 au 15/12/25</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr"/>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr"/>
-      <c r="F14" s="17" t="inlineStr"/>
-      <c r="G14" s="17" t="inlineStr"/>
-      <c r="H14" s="48" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="A14" s="43" t="n"/>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="17" t="n"/>
+      <c r="H14" s="48" t="n"/>
     </row>
     <row r="15" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A15" s="43" t="inlineStr">
-        <is>
-          <t>Travail en mode projet : conduite d'un projet de groupe avec planification et suivi</t>
-        </is>
-      </c>
-      <c r="B15" s="44" t="inlineStr">
-        <is>
-          <t>16/12/25 au 31/01/26</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr"/>
-      <c r="D15" s="17" t="inlineStr"/>
-      <c r="E15" s="17" t="inlineStr"/>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr"/>
-      <c r="H15" s="48" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="A15" s="43" t="n"/>
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="48" t="n"/>
     </row>
     <row r="16" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A16" s="43" t="inlineStr">
-        <is>
-          <t>Veille technologique sur les nouvelles solutions de virtualisation et cybersécurité</t>
-        </is>
-      </c>
-      <c r="B16" s="44" t="inlineStr">
-        <is>
-          <t>01/02/26 au 15/02/26</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr"/>
-      <c r="D16" s="17" t="inlineStr"/>
-      <c r="E16" s="17" t="inlineStr"/>
-      <c r="F16" s="17" t="inlineStr"/>
-      <c r="G16" s="17" t="inlineStr"/>
-      <c r="H16" s="48" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="A16" s="43" t="n"/>
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="17" t="n"/>
+      <c r="H16" s="48" t="n"/>
     </row>
     <row r="17" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A17" s="43" t="inlineStr"/>
-      <c r="B17" s="44" t="inlineStr"/>
-      <c r="C17" s="17" t="inlineStr"/>
-      <c r="D17" s="17" t="inlineStr"/>
-      <c r="E17" s="17" t="inlineStr"/>
-      <c r="F17" s="17" t="inlineStr"/>
-      <c r="G17" s="17" t="inlineStr"/>
-      <c r="H17" s="48" t="inlineStr"/>
+      <c r="A17" s="43" t="n"/>
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
+      <c r="G17" s="17" t="n"/>
+      <c r="H17" s="48" t="n"/>
     </row>
     <row r="18" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A18" s="9" t="inlineStr"/>
-      <c r="B18" s="8" t="inlineStr"/>
-      <c r="C18" s="11" t="inlineStr"/>
-      <c r="D18" s="11" t="inlineStr"/>
-      <c r="E18" s="11" t="inlineStr"/>
-      <c r="F18" s="11" t="inlineStr"/>
-      <c r="G18" s="11" t="inlineStr"/>
-      <c r="H18" s="18" t="inlineStr"/>
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="18" t="n"/>
     </row>
     <row r="19" ht="17.4" customFormat="1" customHeight="1" s="2">
       <c r="A19" s="27" t="inlineStr">
@@ -1584,166 +1460,74 @@
       <c r="H19" s="56" t="n"/>
     </row>
     <row r="20" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>Support informatique de niveau 1 : assistance quotidienne aux collaborateurs (matériel, logiciels, accès)</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>15/09/25 au 30/09/25</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr"/>
-      <c r="F20" s="11" t="inlineStr"/>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr"/>
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="18" t="n"/>
     </row>
     <row r="21" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A21" s="43" t="inlineStr">
-        <is>
-          <t>Gestion et suivi des tickets d'incidents informatiques via l'outil de support de l'entreprise</t>
-        </is>
-      </c>
-      <c r="B21" s="44" t="inlineStr">
-        <is>
-          <t>01/10/25 au 31/10/25</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr"/>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr"/>
-      <c r="F21" s="17" t="inlineStr"/>
-      <c r="G21" s="17" t="inlineStr"/>
-      <c r="H21" s="17" t="inlineStr"/>
+      <c r="A21" s="43" t="n"/>
+      <c r="B21" s="44" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="17" t="n"/>
+      <c r="H21" s="17" t="n"/>
     </row>
     <row r="22" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A22" s="43" t="inlineStr">
-        <is>
-          <t>Participation à la mise à jour et au référencement du site internet de l'entreprise</t>
-        </is>
-      </c>
-      <c r="B22" s="45" t="inlineStr">
-        <is>
-          <t>01/11/25 au 30/11/25</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr"/>
-      <c r="D22" s="17" t="inlineStr"/>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr"/>
-      <c r="G22" s="17" t="inlineStr"/>
-      <c r="H22" s="17" t="inlineStr"/>
+      <c r="A22" s="43" t="n"/>
+      <c r="B22" s="45" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="17" t="n"/>
+      <c r="H22" s="17" t="n"/>
     </row>
     <row r="23" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A23" s="43" t="inlineStr">
-        <is>
-          <t>Aide à la création de plaquettes commerciales et supports de communication numérique</t>
-        </is>
-      </c>
-      <c r="B23" s="44" t="inlineStr">
-        <is>
-          <t>01/12/25 au 31/12/25</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr"/>
-      <c r="D23" s="17" t="inlineStr"/>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr"/>
-      <c r="G23" s="17" t="inlineStr"/>
-      <c r="H23" s="17" t="inlineStr"/>
+      <c r="A23" s="43" t="n"/>
+      <c r="B23" s="44" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="17" t="n"/>
+      <c r="H23" s="17" t="n"/>
     </row>
     <row r="24" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>Installation et configuration de postes de travail pour de nouveaux collaborateurs</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>01/01/26 au 31/01/26</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr"/>
-      <c r="F24" s="11" t="inlineStr"/>
-      <c r="G24" s="11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr"/>
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="18" t="n"/>
     </row>
     <row r="25" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Participation à un projet de migration d'infrastructure (suivi de planning, tests)</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>01/02/26 au 28/02/26</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr"/>
-      <c r="D25" s="11" t="inlineStr"/>
-      <c r="E25" s="11" t="inlineStr"/>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr"/>
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="18" t="n"/>
     </row>
     <row r="26" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A26" s="9" t="inlineStr"/>
-      <c r="B26" s="8" t="inlineStr"/>
-      <c r="C26" s="11" t="inlineStr"/>
-      <c r="D26" s="11" t="inlineStr"/>
-      <c r="E26" s="11" t="inlineStr"/>
-      <c r="F26" s="11" t="inlineStr"/>
-      <c r="G26" s="11" t="inlineStr"/>
-      <c r="H26" s="18" t="inlineStr"/>
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="18" t="n"/>
     </row>
     <row r="27" ht="17.4" customFormat="1" customHeight="1" s="2">
       <c r="A27" s="27" t="inlineStr">
@@ -1760,11 +1544,7 @@
       <c r="H27" s="56" t="n"/>
     </row>
     <row r="28" ht="39.9" customFormat="1" customHeight="1" s="2">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>(à compléter en 2ème année - 2026/2027)</t>
-        </is>
-      </c>
+      <c r="A28" s="9" t="n"/>
       <c r="B28" s="8" t="n"/>
       <c r="C28" s="19" t="n"/>
       <c r="D28" s="19" t="n"/>
@@ -1823,6 +1603,52 @@
       <c r="G33" s="4" t="n"/>
       <c r="H33" s="4" t="n"/>
     </row>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A4:E4"/>
